--- a/dist/成果/防治对象/测量表/360481106205112_铺头村邓家坝/沟道纵断面成果表_AFAE90012A000000ZACS004.xlsx
+++ b/dist/成果/防治对象/测量表/360481106205112_铺头村邓家坝/沟道纵断面成果表_AFAE90012A000000ZACS004.xlsx
@@ -822,7 +822,7 @@
         <v>43.355</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>43.77677197486403</v>
+        <v>43.534821410723</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.517934</v>
@@ -850,7 +850,7 @@
         <v>43.264</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>43.3111105585305</v>
+        <v>43.48091905650696</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.518827</v>
@@ -878,7 +878,7 @@
         <v>42.818</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>43.03138462403268</v>
+        <v>43.20413762588093</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.519622</v>
@@ -906,7 +906,7 @@
         <v>42.527</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>42.77251311130685</v>
+        <v>43.14001685775461</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.520587</v>
@@ -934,7 +934,7 @@
         <v>42.495</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>42.93453657771344</v>
+        <v>42.94547263787897</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.521541</v>
@@ -962,7 +962,7 @@
         <v>42.093</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>42.49337300977104</v>
+        <v>42.57537814260128</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.521811</v>
@@ -990,7 +990,7 @@
         <v>42.118</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>42.42479423371082</v>
+        <v>42.21151989088373</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.522376</v>
@@ -1018,7 +1018,7 @@
         <v>42.116</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>42.37195953826244</v>
+        <v>42.20369522972015</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.522945</v>
@@ -1046,7 +1046,7 @@
         <v>42.097</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>42.29867494949016</v>
+        <v>42.18805024257959</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.523492</v>
@@ -1074,7 +1074,7 @@
         <v>42.098</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>42.17822923292453</v>
+        <v>42.16843348715069</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.523986</v>
@@ -1102,7 +1102,7 @@
         <v>42.087</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>42.12017545008516</v>
+        <v>42.43174245867041</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.524556</v>
@@ -1130,7 +1130,7 @@
         <v>41.967</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>42.04104112838976</v>
+        <v>42.28457977698845</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.525186</v>
@@ -1158,7 +1158,7 @@
         <v>41.841</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>42.19533775660848</v>
+        <v>41.97350672238557</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.525696</v>
@@ -1186,7 +1186,7 @@
         <v>41.727</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>42.13717555601236</v>
+        <v>41.9515008679157</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.526195</v>
@@ -1238,16 +1238,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
